--- a/artfynd/A 63946-2025 artfynd.xlsx
+++ b/artfynd/A 63946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128947254</v>
       </c>
       <c r="B2" t="n">
-        <v>91571</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,6 +779,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128947256</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenstorps Hagkärr, SO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>578451</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6520211</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63946-2025 artfynd.xlsx
+++ b/artfynd/A 63946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947254</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>